--- a/typing_analysis_1778543727.xlsx
+++ b/typing_analysis_1778543727.xlsx
@@ -11,6 +11,7 @@
     <sheet name="3gram_全データ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3gram_集計" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="パターン別サマリ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="母音パターン別サマリ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +473,11 @@
           <t>session_id</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>boin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -506,6 +512,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -540,6 +549,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -574,6 +586,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -608,6 +623,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -642,6 +660,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -676,6 +697,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -710,6 +734,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -744,6 +771,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -778,6 +808,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -812,6 +845,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -846,6 +882,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -880,6 +919,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -914,6 +956,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -948,6 +993,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -982,6 +1030,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1016,6 +1067,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1050,6 +1104,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1084,6 +1141,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1118,6 +1178,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1152,6 +1215,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1186,6 +1252,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1220,6 +1289,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1254,6 +1326,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1288,6 +1363,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1322,6 +1400,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1356,6 +1437,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1390,6 +1474,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1424,6 +1511,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1458,6 +1548,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1492,6 +1585,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1526,6 +1622,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1560,6 +1659,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1594,6 +1696,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1628,6 +1733,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1662,6 +1770,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1696,6 +1807,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1730,6 +1844,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1764,6 +1881,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1798,6 +1918,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1832,6 +1955,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1866,6 +1992,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1900,6 +2029,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1934,6 +2066,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1968,6 +2103,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2002,6 +2140,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2036,6 +2177,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2070,6 +2214,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2104,6 +2251,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2138,6 +2288,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2172,6 +2325,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2206,6 +2362,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2240,6 +2399,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2274,6 +2436,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2308,6 +2473,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2342,6 +2510,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2376,6 +2547,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2410,6 +2584,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2444,6 +2621,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2478,6 +2658,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2512,6 +2695,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2546,6 +2732,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2580,6 +2769,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2614,6 +2806,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2648,6 +2843,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2682,6 +2880,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2716,6 +2917,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2750,6 +2954,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2784,6 +2991,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2818,6 +3028,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2852,6 +3065,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2886,6 +3102,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2920,6 +3139,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2954,6 +3176,9 @@
           <t>1778543727</t>
         </is>
       </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2987,6 +3212,9 @@
         <is>
           <t>1778543727</t>
         </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3000,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:X73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3056,40 +3284,70 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>key_1_type</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>key_2_type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>key_3_type</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>vowel_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>vowel_pattern</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>hand_pattern</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>interval_1_2_ms</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>interval_2_3_ms</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>avg_interval_ms</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>has_error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>same_finger</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>same_hand_all</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>alternating</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pattern_type</t>
         </is>
@@ -3146,28 +3404,56 @@
           <t>r</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>182</v>
       </c>
-      <c r="L2" t="n">
+      <c r="R2" t="n">
         <v>219</v>
       </c>
-      <c r="M2" t="n">
+      <c r="S2" t="n">
         <v>200.5</v>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -3224,28 +3510,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
         <v>219</v>
       </c>
-      <c r="L3" t="n">
+      <c r="R3" t="n">
         <v>101</v>
       </c>
-      <c r="M3" t="n">
+      <c r="S3" t="n">
         <v>160</v>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -3302,28 +3616,56 @@
           <t>g</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>101</v>
       </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
         <v>164</v>
       </c>
-      <c r="M4" t="n">
+      <c r="S4" t="n">
         <v>132.5</v>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -3380,28 +3722,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>164</v>
       </c>
-      <c r="L5" t="n">
+      <c r="R5" t="n">
         <v>71</v>
       </c>
-      <c r="M5" t="n">
+      <c r="S5" t="n">
         <v>117.5</v>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -3458,28 +3828,56 @@
           <t>d</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>71</v>
       </c>
-      <c r="L6" t="n">
+      <c r="R6" t="n">
         <v>228</v>
       </c>
-      <c r="M6" t="n">
+      <c r="S6" t="n">
         <v>149.5</v>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -3536,28 +3934,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>228</v>
       </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
         <v>71</v>
       </c>
-      <c r="M7" t="n">
+      <c r="S7" t="n">
         <v>149.5</v>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -3614,28 +4040,56 @@
           <t>y</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
         <v>71</v>
       </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
         <v>159</v>
       </c>
-      <c r="M8" t="n">
+      <c r="S8" t="n">
         <v>115</v>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -3692,28 +4146,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>159</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
         <v>63</v>
       </c>
-      <c r="M9" t="n">
+      <c r="S9" t="n">
         <v>111</v>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -3770,28 +4252,56 @@
           <t>i</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
         <v>63</v>
       </c>
-      <c r="L10" t="n">
+      <c r="R10" t="n">
         <v>880</v>
       </c>
-      <c r="M10" t="n">
+      <c r="S10" t="n">
         <v>471.5</v>
       </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -3848,28 +4358,56 @@
           <t>r</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
         <v>880</v>
       </c>
-      <c r="L11" t="n">
+      <c r="R11" t="n">
         <v>85</v>
       </c>
-      <c r="M11" t="n">
+      <c r="S11" t="n">
         <v>482.5</v>
       </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -3926,28 +4464,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
         <v>85</v>
       </c>
-      <c r="L12" t="n">
+      <c r="R12" t="n">
         <v>82</v>
       </c>
-      <c r="M12" t="n">
+      <c r="S12" t="n">
         <v>83.5</v>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -4004,28 +4570,56 @@
           <t>i</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
         <v>82</v>
       </c>
-      <c r="L13" t="n">
+      <c r="R13" t="n">
         <v>78</v>
       </c>
-      <c r="M13" t="n">
+      <c r="S13" t="n">
         <v>80</v>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4082,28 +4676,56 @@
           <t>r</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
         <v>78</v>
       </c>
-      <c r="L14" t="n">
+      <c r="R14" t="n">
         <v>88</v>
       </c>
-      <c r="M14" t="n">
+      <c r="S14" t="n">
         <v>83</v>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4160,28 +4782,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
         <v>88</v>
       </c>
-      <c r="L15" t="n">
+      <c r="R15" t="n">
         <v>84</v>
       </c>
-      <c r="M15" t="n">
+      <c r="S15" t="n">
         <v>86</v>
       </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -4238,28 +4888,56 @@
           <t>h</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
         <v>84</v>
       </c>
-      <c r="L16" t="n">
+      <c r="R16" t="n">
         <v>1330</v>
       </c>
-      <c r="M16" t="n">
+      <c r="S16" t="n">
         <v>707</v>
       </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4316,28 +4994,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
         <v>1330</v>
       </c>
-      <c r="L17" t="n">
+      <c r="R17" t="n">
         <v>90</v>
       </c>
-      <c r="M17" t="n">
+      <c r="S17" t="n">
         <v>710</v>
       </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4394,28 +5100,56 @@
           <t>i</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
         <v>90</v>
       </c>
-      <c r="L18" t="n">
+      <c r="R18" t="n">
         <v>83</v>
       </c>
-      <c r="M18" t="n">
+      <c r="S18" t="n">
         <v>86.5</v>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -4472,28 +5206,56 @@
           <t>r</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
         <v>83</v>
       </c>
-      <c r="L19" t="n">
+      <c r="R19" t="n">
         <v>100</v>
       </c>
-      <c r="M19" t="n">
+      <c r="S19" t="n">
         <v>91.5</v>
       </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -4550,28 +5312,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
         <v>100</v>
       </c>
-      <c r="L20" t="n">
+      <c r="R20" t="n">
         <v>44</v>
       </c>
-      <c r="M20" t="n">
+      <c r="S20" t="n">
         <v>72</v>
       </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4628,28 +5418,56 @@
           <t>t</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
         <v>44</v>
       </c>
-      <c r="L21" t="n">
+      <c r="R21" t="n">
         <v>152</v>
       </c>
-      <c r="M21" t="n">
+      <c r="S21" t="n">
         <v>98</v>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -4706,28 +5524,56 @@
           <t>u</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
         <v>152</v>
       </c>
-      <c r="L22" t="n">
+      <c r="R22" t="n">
         <v>71</v>
       </c>
-      <c r="M22" t="n">
+      <c r="S22" t="n">
         <v>111.5</v>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4784,28 +5630,56 @@
           <t>g</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
         <v>71</v>
       </c>
-      <c r="L23" t="n">
+      <c r="R23" t="n">
         <v>146</v>
       </c>
-      <c r="M23" t="n">
+      <c r="S23" t="n">
         <v>108.5</v>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -4862,28 +5736,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
         <v>146</v>
       </c>
-      <c r="L24" t="n">
+      <c r="R24" t="n">
         <v>66</v>
       </c>
-      <c r="M24" t="n">
+      <c r="S24" t="n">
         <v>106</v>
       </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
-      <c r="O24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -4940,28 +5842,56 @@
           <t>t</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
         <v>66</v>
       </c>
-      <c r="L25" t="n">
+      <c r="R25" t="n">
         <v>186</v>
       </c>
-      <c r="M25" t="n">
+      <c r="S25" t="n">
         <v>126</v>
       </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -5018,28 +5948,56 @@
           <t>i</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
         <v>186</v>
       </c>
-      <c r="L26" t="n">
+      <c r="R26" t="n">
         <v>64</v>
       </c>
-      <c r="M26" t="n">
+      <c r="S26" t="n">
         <v>125</v>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -5096,28 +6054,56 @@
           <t>g</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
         <v>64</v>
       </c>
-      <c r="L27" t="n">
+      <c r="R27" t="n">
         <v>105</v>
       </c>
-      <c r="M27" t="n">
+      <c r="S27" t="n">
         <v>84.5</v>
       </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -5174,28 +6160,56 @@
           <t>u</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
         <v>105</v>
       </c>
-      <c r="L28" t="n">
+      <c r="R28" t="n">
         <v>109</v>
       </c>
-      <c r="M28" t="n">
+      <c r="S28" t="n">
         <v>107</v>
       </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
-      <c r="O28" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -5252,28 +6266,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
         <v>109</v>
       </c>
-      <c r="L29" t="n">
+      <c r="R29" t="n">
         <v>7</v>
       </c>
-      <c r="M29" t="n">
+      <c r="S29" t="n">
         <v>58</v>
       </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -5330,28 +6372,56 @@
           <t>k</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
         <v>7</v>
       </c>
-      <c r="L30" t="n">
+      <c r="R30" t="n">
         <v>179</v>
       </c>
-      <c r="M30" t="n">
+      <c r="S30" t="n">
         <v>93</v>
       </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30" t="b">
-        <v>0</v>
-      </c>
-      <c r="P30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -5408,28 +6478,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
         <v>179</v>
       </c>
-      <c r="L31" t="n">
+      <c r="R31" t="n">
         <v>75</v>
       </c>
-      <c r="M31" t="n">
+      <c r="S31" t="n">
         <v>127</v>
       </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31" t="b">
-        <v>0</v>
-      </c>
-      <c r="P31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -5486,28 +6584,56 @@
           <t>r</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
         <v>75</v>
       </c>
-      <c r="L32" t="n">
+      <c r="R32" t="n">
         <v>166</v>
       </c>
-      <c r="M32" t="n">
+      <c r="S32" t="n">
         <v>120.5</v>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" t="b">
-        <v>0</v>
-      </c>
-      <c r="P32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -5564,28 +6690,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
         <v>166</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>83</v>
       </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
-      <c r="O33" t="b">
-        <v>0</v>
-      </c>
-      <c r="P33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -5642,28 +6796,56 @@
           <t>t</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>474</v>
       </c>
-      <c r="M34" t="n">
+      <c r="S34" t="n">
         <v>237</v>
       </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O34" t="b">
-        <v>0</v>
-      </c>
-      <c r="P34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -5720,28 +6902,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
         <v>474</v>
       </c>
-      <c r="L35" t="n">
+      <c r="R35" t="n">
         <v>60</v>
       </c>
-      <c r="M35" t="n">
+      <c r="S35" t="n">
         <v>267</v>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" t="b">
-        <v>0</v>
-      </c>
-      <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="W35" t="b">
+        <v>0</v>
+      </c>
+      <c r="X35" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -5798,28 +7008,56 @@
           <t>i</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
         <v>60</v>
       </c>
-      <c r="L36" t="n">
+      <c r="R36" t="n">
         <v>71</v>
       </c>
-      <c r="M36" t="n">
+      <c r="S36" t="n">
         <v>65.5</v>
       </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
-      <c r="O36" t="b">
-        <v>0</v>
-      </c>
-      <c r="P36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" t="inlineStr">
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -5876,28 +7114,56 @@
           <t>h</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
         <v>71</v>
       </c>
-      <c r="L37" t="n">
+      <c r="R37" t="n">
         <v>165</v>
       </c>
-      <c r="M37" t="n">
+      <c r="S37" t="n">
         <v>118</v>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
-      <c r="O37" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -5954,28 +7220,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
         <v>165</v>
       </c>
-      <c r="L38" t="n">
+      <c r="R38" t="n">
         <v>69</v>
       </c>
-      <c r="M38" t="n">
+      <c r="S38" t="n">
         <v>117</v>
       </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
-      <c r="O38" t="b">
-        <v>0</v>
-      </c>
-      <c r="P38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="b">
+        <v>0</v>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -6032,28 +7326,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
         <v>69</v>
       </c>
-      <c r="L39" t="n">
+      <c r="R39" t="n">
         <v>139</v>
       </c>
-      <c r="M39" t="n">
+      <c r="S39" t="n">
         <v>104</v>
       </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
-      <c r="O39" t="b">
-        <v>0</v>
-      </c>
-      <c r="P39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>1</v>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -6110,28 +7432,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>VCC</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
         <v>139</v>
       </c>
-      <c r="L40" t="n">
+      <c r="R40" t="n">
         <v>117</v>
       </c>
-      <c r="M40" t="n">
+      <c r="S40" t="n">
         <v>128</v>
       </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
-      <c r="O40" t="b">
-        <v>1</v>
-      </c>
-      <c r="P40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>1</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="b">
+        <v>0</v>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -6188,28 +7538,56 @@
           <t>d</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
         <v>117</v>
       </c>
-      <c r="L41" t="n">
+      <c r="R41" t="n">
         <v>78</v>
       </c>
-      <c r="M41" t="n">
+      <c r="S41" t="n">
         <v>97.5</v>
       </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
-      <c r="O41" t="b">
-        <v>1</v>
-      </c>
-      <c r="P41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>1</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="b">
+        <v>0</v>
+      </c>
+      <c r="X41" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -6266,28 +7644,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>CCV</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
         <v>78</v>
       </c>
-      <c r="L42" t="n">
+      <c r="R42" t="n">
         <v>64</v>
       </c>
-      <c r="M42" t="n">
+      <c r="S42" t="n">
         <v>71</v>
       </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
-      <c r="O42" t="b">
-        <v>0</v>
-      </c>
-      <c r="P42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="b">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -6344,28 +7750,56 @@
           <t>k</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
         <v>64</v>
       </c>
-      <c r="L43" t="n">
+      <c r="R43" t="n">
         <v>61</v>
       </c>
-      <c r="M43" t="n">
+      <c r="S43" t="n">
         <v>62.5</v>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
-      <c r="O43" t="b">
-        <v>0</v>
-      </c>
-      <c r="P43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="b">
-        <v>0</v>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="T43" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="b">
+        <v>0</v>
+      </c>
+      <c r="X43" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -6422,28 +7856,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
         <v>61</v>
       </c>
-      <c r="L44" t="n">
+      <c r="R44" t="n">
         <v>97</v>
       </c>
-      <c r="M44" t="n">
+      <c r="S44" t="n">
         <v>79</v>
       </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
-      <c r="O44" t="b">
-        <v>0</v>
-      </c>
-      <c r="P44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="b">
-        <v>1</v>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="T44" t="b">
+        <v>0</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -6500,28 +7962,56 @@
           <t>d</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
         <v>97</v>
       </c>
-      <c r="L45" t="n">
+      <c r="R45" t="n">
         <v>149</v>
       </c>
-      <c r="M45" t="n">
+      <c r="S45" t="n">
         <v>123</v>
       </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
-      <c r="O45" t="b">
-        <v>1</v>
-      </c>
-      <c r="P45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>1</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45" t="b">
+        <v>0</v>
+      </c>
+      <c r="X45" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -6578,28 +8068,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
         <v>149</v>
       </c>
-      <c r="L46" t="n">
+      <c r="R46" t="n">
         <v>86</v>
       </c>
-      <c r="M46" t="n">
+      <c r="S46" t="n">
         <v>117.5</v>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
-      <c r="O46" t="b">
-        <v>1</v>
-      </c>
-      <c r="P46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="b">
-        <v>0</v>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="T46" t="b">
+        <v>0</v>
+      </c>
+      <c r="U46" t="b">
+        <v>1</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="b">
+        <v>0</v>
+      </c>
+      <c r="X46" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -6656,28 +8174,56 @@
           <t>s</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
         <v>86</v>
       </c>
-      <c r="L47" t="n">
+      <c r="R47" t="n">
         <v>131</v>
       </c>
-      <c r="M47" t="n">
+      <c r="S47" t="n">
         <v>108.5</v>
       </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-      <c r="O47" t="b">
-        <v>0</v>
-      </c>
-      <c r="P47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="b">
-        <v>1</v>
-      </c>
-      <c r="R47" t="inlineStr">
+      <c r="T47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="b">
+        <v>1</v>
+      </c>
+      <c r="X47" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -6734,28 +8280,56 @@
           <t>i</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
         <v>131</v>
       </c>
-      <c r="L48" t="n">
+      <c r="R48" t="n">
         <v>102</v>
       </c>
-      <c r="M48" t="n">
+      <c r="S48" t="n">
         <v>116.5</v>
       </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O48" t="b">
-        <v>0</v>
-      </c>
-      <c r="P48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="b">
-        <v>1</v>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="T48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
+      <c r="W48" t="b">
+        <v>1</v>
+      </c>
+      <c r="X48" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -6812,28 +8386,56 @@
           <t>z</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
         <v>102</v>
       </c>
-      <c r="L49" t="n">
+      <c r="R49" t="n">
         <v>159</v>
       </c>
-      <c r="M49" t="n">
+      <c r="S49" t="n">
         <v>130.5</v>
       </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
-      <c r="O49" t="b">
-        <v>0</v>
-      </c>
-      <c r="P49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>1</v>
-      </c>
-      <c r="R49" t="inlineStr">
+      <c r="T49" t="b">
+        <v>0</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="b">
+        <v>1</v>
+      </c>
+      <c r="X49" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -6890,28 +8492,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K50" t="n">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
         <v>159</v>
       </c>
-      <c r="L50" t="n">
+      <c r="R50" t="n">
         <v>65</v>
       </c>
-      <c r="M50" t="n">
+      <c r="S50" t="n">
         <v>112</v>
       </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
-      <c r="O50" t="b">
-        <v>0</v>
-      </c>
-      <c r="P50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="b">
-        <v>0</v>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="T50" t="b">
+        <v>0</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
+      <c r="W50" t="b">
+        <v>0</v>
+      </c>
+      <c r="X50" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -6968,28 +8598,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
         <v>65</v>
       </c>
-      <c r="L51" t="n">
+      <c r="R51" t="n">
         <v>77</v>
       </c>
-      <c r="M51" t="n">
+      <c r="S51" t="n">
         <v>71</v>
       </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" t="b">
-        <v>0</v>
-      </c>
-      <c r="P51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="b">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="T51" t="b">
+        <v>0</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
+      <c r="W51" t="b">
+        <v>0</v>
+      </c>
+      <c r="X51" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -7046,28 +8704,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>VCC</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
         <v>77</v>
       </c>
-      <c r="L52" t="n">
+      <c r="R52" t="n">
         <v>116</v>
       </c>
-      <c r="M52" t="n">
+      <c r="S52" t="n">
         <v>96.5</v>
       </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
-      <c r="O52" t="b">
-        <v>1</v>
-      </c>
-      <c r="P52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="b">
-        <v>0</v>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="T52" t="b">
+        <v>0</v>
+      </c>
+      <c r="U52" t="b">
+        <v>1</v>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="b">
+        <v>0</v>
+      </c>
+      <c r="X52" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -7124,28 +8810,56 @@
           <t>g</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
         <v>116</v>
       </c>
-      <c r="L53" t="n">
+      <c r="R53" t="n">
         <v>117</v>
       </c>
-      <c r="M53" t="n">
+      <c r="S53" t="n">
         <v>116.5</v>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
-      <c r="O53" t="b">
-        <v>1</v>
-      </c>
-      <c r="P53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="b">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr">
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <v>1</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="b">
+        <v>0</v>
+      </c>
+      <c r="X53" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -7202,28 +8916,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K54" t="n">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>CCV</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
         <v>117</v>
       </c>
-      <c r="L54" t="n">
+      <c r="R54" t="n">
         <v>51</v>
       </c>
-      <c r="M54" t="n">
+      <c r="S54" t="n">
         <v>84</v>
       </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
-      <c r="O54" t="b">
-        <v>0</v>
-      </c>
-      <c r="P54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="b">
-        <v>0</v>
-      </c>
-      <c r="R54" t="inlineStr">
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54" t="b">
+        <v>0</v>
+      </c>
+      <c r="W54" t="b">
+        <v>0</v>
+      </c>
+      <c r="X54" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -7280,28 +9022,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
         <v>51</v>
       </c>
-      <c r="L55" t="n">
+      <c r="R55" t="n">
         <v>67</v>
       </c>
-      <c r="M55" t="n">
+      <c r="S55" t="n">
         <v>59</v>
       </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
-      <c r="O55" t="b">
-        <v>0</v>
-      </c>
-      <c r="P55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="b">
-        <v>0</v>
-      </c>
-      <c r="R55" t="inlineStr">
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+      <c r="V55" t="b">
+        <v>0</v>
+      </c>
+      <c r="W55" t="b">
+        <v>0</v>
+      </c>
+      <c r="X55" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -7358,28 +9128,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K56" t="n">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>VCC</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
         <v>67</v>
       </c>
-      <c r="L56" t="n">
+      <c r="R56" t="n">
         <v>114</v>
       </c>
-      <c r="M56" t="n">
+      <c r="S56" t="n">
         <v>90.5</v>
       </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
-      <c r="O56" t="b">
-        <v>1</v>
-      </c>
-      <c r="P56" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="b">
-        <v>0</v>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="T56" t="b">
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <v>1</v>
+      </c>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
+      <c r="W56" t="b">
+        <v>0</v>
+      </c>
+      <c r="X56" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -7436,28 +9234,56 @@
           <t>g</t>
         </is>
       </c>
-      <c r="K57" t="n">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
         <v>114</v>
       </c>
-      <c r="L57" t="n">
+      <c r="R57" t="n">
         <v>99</v>
       </c>
-      <c r="M57" t="n">
+      <c r="S57" t="n">
         <v>106.5</v>
       </c>
-      <c r="N57" t="b">
-        <v>0</v>
-      </c>
-      <c r="O57" t="b">
-        <v>1</v>
-      </c>
-      <c r="P57" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="b">
-        <v>0</v>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="T57" t="b">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>1</v>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="b">
+        <v>0</v>
+      </c>
+      <c r="X57" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -7514,28 +9340,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K58" t="n">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>CCV</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
         <v>99</v>
       </c>
-      <c r="L58" t="n">
+      <c r="R58" t="n">
         <v>121</v>
       </c>
-      <c r="M58" t="n">
+      <c r="S58" t="n">
         <v>110</v>
       </c>
-      <c r="N58" t="b">
-        <v>0</v>
-      </c>
-      <c r="O58" t="b">
-        <v>0</v>
-      </c>
-      <c r="P58" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="b">
-        <v>1</v>
-      </c>
-      <c r="R58" t="inlineStr">
+      <c r="T58" t="b">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58" t="b">
+        <v>0</v>
+      </c>
+      <c r="W58" t="b">
+        <v>1</v>
+      </c>
+      <c r="X58" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -7592,28 +9446,56 @@
           <t>t</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
         <v>121</v>
       </c>
-      <c r="L59" t="n">
+      <c r="R59" t="n">
         <v>320</v>
       </c>
-      <c r="M59" t="n">
+      <c r="S59" t="n">
         <v>220.5</v>
       </c>
-      <c r="N59" t="b">
-        <v>0</v>
-      </c>
-      <c r="O59" t="b">
-        <v>0</v>
-      </c>
-      <c r="P59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="b">
-        <v>1</v>
-      </c>
-      <c r="R59" t="inlineStr">
+      <c r="T59" t="b">
+        <v>0</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+      <c r="V59" t="b">
+        <v>0</v>
+      </c>
+      <c r="W59" t="b">
+        <v>1</v>
+      </c>
+      <c r="X59" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -7670,28 +9552,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K60" t="n">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
         <v>320</v>
       </c>
-      <c r="L60" t="n">
+      <c r="R60" t="n">
         <v>62</v>
       </c>
-      <c r="M60" t="n">
+      <c r="S60" t="n">
         <v>191</v>
       </c>
-      <c r="N60" t="b">
-        <v>0</v>
-      </c>
-      <c r="O60" t="b">
-        <v>0</v>
-      </c>
-      <c r="P60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="b">
-        <v>1</v>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="T60" t="b">
+        <v>0</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+      <c r="V60" t="b">
+        <v>0</v>
+      </c>
+      <c r="W60" t="b">
+        <v>1</v>
+      </c>
+      <c r="X60" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -7748,28 +9658,56 @@
           <t>k</t>
         </is>
       </c>
-      <c r="K61" t="n">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
         <v>62</v>
       </c>
-      <c r="L61" t="n">
+      <c r="R61" t="n">
         <v>163</v>
       </c>
-      <c r="M61" t="n">
+      <c r="S61" t="n">
         <v>112.5</v>
       </c>
-      <c r="N61" t="b">
-        <v>0</v>
-      </c>
-      <c r="O61" t="b">
-        <v>0</v>
-      </c>
-      <c r="P61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="b">
-        <v>0</v>
-      </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="b">
+        <v>0</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+      <c r="V61" t="b">
+        <v>0</v>
+      </c>
+      <c r="W61" t="b">
+        <v>0</v>
+      </c>
+      <c r="X61" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -7826,28 +9764,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K62" t="n">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
         <v>163</v>
       </c>
-      <c r="L62" t="n">
+      <c r="R62" t="n">
         <v>64</v>
       </c>
-      <c r="M62" t="n">
+      <c r="S62" t="n">
         <v>113.5</v>
       </c>
-      <c r="N62" t="b">
-        <v>0</v>
-      </c>
-      <c r="O62" t="b">
-        <v>0</v>
-      </c>
-      <c r="P62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="b">
-        <v>0</v>
-      </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="b">
+        <v>0</v>
+      </c>
+      <c r="U62" t="b">
+        <v>0</v>
+      </c>
+      <c r="V62" t="b">
+        <v>0</v>
+      </c>
+      <c r="W62" t="b">
+        <v>0</v>
+      </c>
+      <c r="X62" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -7904,28 +9870,56 @@
           <t>d</t>
         </is>
       </c>
-      <c r="K63" t="n">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
         <v>64</v>
       </c>
-      <c r="L63" t="n">
+      <c r="R63" t="n">
         <v>153</v>
       </c>
-      <c r="M63" t="n">
+      <c r="S63" t="n">
         <v>108.5</v>
       </c>
-      <c r="N63" t="b">
-        <v>0</v>
-      </c>
-      <c r="O63" t="b">
-        <v>0</v>
-      </c>
-      <c r="P63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="b">
-        <v>0</v>
-      </c>
-      <c r="R63" t="inlineStr">
+      <c r="T63" t="b">
+        <v>0</v>
+      </c>
+      <c r="U63" t="b">
+        <v>0</v>
+      </c>
+      <c r="V63" t="b">
+        <v>0</v>
+      </c>
+      <c r="W63" t="b">
+        <v>0</v>
+      </c>
+      <c r="X63" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -7982,28 +9976,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K64" t="n">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>LLL</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
         <v>153</v>
       </c>
-      <c r="L64" t="n">
+      <c r="R64" t="n">
         <v>216</v>
       </c>
-      <c r="M64" t="n">
+      <c r="S64" t="n">
         <v>184.5</v>
       </c>
-      <c r="N64" t="b">
-        <v>0</v>
-      </c>
-      <c r="O64" t="b">
-        <v>1</v>
-      </c>
-      <c r="P64" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q64" t="b">
-        <v>0</v>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="T64" t="b">
+        <v>0</v>
+      </c>
+      <c r="U64" t="b">
+        <v>1</v>
+      </c>
+      <c r="V64" t="b">
+        <v>1</v>
+      </c>
+      <c r="W64" t="b">
+        <v>0</v>
+      </c>
+      <c r="X64" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -8060,28 +10082,56 @@
           <t>y</t>
         </is>
       </c>
-      <c r="K65" t="n">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
         <v>216</v>
       </c>
-      <c r="L65" t="n">
+      <c r="R65" t="n">
         <v>218</v>
       </c>
-      <c r="M65" t="n">
+      <c r="S65" t="n">
         <v>217</v>
       </c>
-      <c r="N65" t="b">
-        <v>0</v>
-      </c>
-      <c r="O65" t="b">
-        <v>1</v>
-      </c>
-      <c r="P65" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="b">
-        <v>0</v>
-      </c>
-      <c r="R65" t="inlineStr">
+      <c r="T65" t="b">
+        <v>0</v>
+      </c>
+      <c r="U65" t="b">
+        <v>1</v>
+      </c>
+      <c r="V65" t="b">
+        <v>0</v>
+      </c>
+      <c r="W65" t="b">
+        <v>0</v>
+      </c>
+      <c r="X65" t="inlineStr">
         <is>
           <t>同指連打</t>
         </is>
@@ -8138,28 +10188,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K66" t="n">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
         <v>218</v>
       </c>
-      <c r="L66" t="n">
+      <c r="R66" t="n">
         <v>85</v>
       </c>
-      <c r="M66" t="n">
+      <c r="S66" t="n">
         <v>151.5</v>
       </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
-      <c r="O66" t="b">
-        <v>0</v>
-      </c>
-      <c r="P66" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="b">
-        <v>1</v>
-      </c>
-      <c r="R66" t="inlineStr">
+      <c r="T66" t="b">
+        <v>0</v>
+      </c>
+      <c r="U66" t="b">
+        <v>0</v>
+      </c>
+      <c r="V66" t="b">
+        <v>0</v>
+      </c>
+      <c r="W66" t="b">
+        <v>1</v>
+      </c>
+      <c r="X66" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -8216,28 +10294,56 @@
           <t>r</t>
         </is>
       </c>
-      <c r="K67" t="n">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>RLL</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
         <v>85</v>
       </c>
-      <c r="L67" t="n">
+      <c r="R67" t="n">
         <v>50</v>
       </c>
-      <c r="M67" t="n">
+      <c r="S67" t="n">
         <v>67.5</v>
       </c>
-      <c r="N67" t="b">
-        <v>0</v>
-      </c>
-      <c r="O67" t="b">
-        <v>0</v>
-      </c>
-      <c r="P67" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="b">
-        <v>0</v>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="T67" t="b">
+        <v>0</v>
+      </c>
+      <c r="U67" t="b">
+        <v>0</v>
+      </c>
+      <c r="V67" t="b">
+        <v>0</v>
+      </c>
+      <c r="W67" t="b">
+        <v>0</v>
+      </c>
+      <c r="X67" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -8294,28 +10400,56 @@
           <t>o</t>
         </is>
       </c>
-      <c r="K68" t="n">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>LLR</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
         <v>50</v>
       </c>
-      <c r="L68" t="n">
+      <c r="R68" t="n">
         <v>84</v>
       </c>
-      <c r="M68" t="n">
+      <c r="S68" t="n">
         <v>67</v>
       </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
-      <c r="O68" t="b">
-        <v>0</v>
-      </c>
-      <c r="P68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="b">
-        <v>0</v>
-      </c>
-      <c r="R68" t="inlineStr">
+      <c r="T68" t="b">
+        <v>0</v>
+      </c>
+      <c r="U68" t="b">
+        <v>0</v>
+      </c>
+      <c r="V68" t="b">
+        <v>0</v>
+      </c>
+      <c r="W68" t="b">
+        <v>0</v>
+      </c>
+      <c r="X68" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -8372,28 +10506,56 @@
           <t>u</t>
         </is>
       </c>
-      <c r="K69" t="n">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>LRR</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
         <v>84</v>
       </c>
-      <c r="L69" t="n">
+      <c r="R69" t="n">
         <v>33</v>
       </c>
-      <c r="M69" t="n">
+      <c r="S69" t="n">
         <v>58.5</v>
       </c>
-      <c r="N69" t="b">
-        <v>0</v>
-      </c>
-      <c r="O69" t="b">
-        <v>0</v>
-      </c>
-      <c r="P69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="b">
-        <v>0</v>
-      </c>
-      <c r="R69" t="inlineStr">
+      <c r="T69" t="b">
+        <v>0</v>
+      </c>
+      <c r="U69" t="b">
+        <v>0</v>
+      </c>
+      <c r="V69" t="b">
+        <v>0</v>
+      </c>
+      <c r="W69" t="b">
+        <v>0</v>
+      </c>
+      <c r="X69" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -8450,28 +10612,56 @@
           <t>k</t>
         </is>
       </c>
-      <c r="K70" t="n">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
         <v>33</v>
       </c>
-      <c r="L70" t="n">
+      <c r="R70" t="n">
         <v>163</v>
       </c>
-      <c r="M70" t="n">
+      <c r="S70" t="n">
         <v>98</v>
       </c>
-      <c r="N70" t="b">
-        <v>0</v>
-      </c>
-      <c r="O70" t="b">
-        <v>0</v>
-      </c>
-      <c r="P70" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="b">
-        <v>0</v>
-      </c>
-      <c r="R70" t="inlineStr">
+      <c r="T70" t="b">
+        <v>0</v>
+      </c>
+      <c r="U70" t="b">
+        <v>0</v>
+      </c>
+      <c r="V70" t="b">
+        <v>1</v>
+      </c>
+      <c r="W70" t="b">
+        <v>0</v>
+      </c>
+      <c r="X70" t="inlineStr">
         <is>
           <t>同手3連</t>
         </is>
@@ -8528,28 +10718,56 @@
           <t>a</t>
         </is>
       </c>
-      <c r="K71" t="n">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>RRL</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
         <v>163</v>
       </c>
-      <c r="L71" t="n">
+      <c r="R71" t="n">
         <v>105</v>
       </c>
-      <c r="M71" t="n">
+      <c r="S71" t="n">
         <v>134</v>
       </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
-      <c r="O71" t="b">
-        <v>0</v>
-      </c>
-      <c r="P71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="b">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr">
+      <c r="T71" t="b">
+        <v>0</v>
+      </c>
+      <c r="U71" t="b">
+        <v>0</v>
+      </c>
+      <c r="V71" t="b">
+        <v>0</v>
+      </c>
+      <c r="W71" t="b">
+        <v>0</v>
+      </c>
+      <c r="X71" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
@@ -8606,28 +10824,56 @@
           <t>n</t>
         </is>
       </c>
-      <c r="K72" t="n">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>RLR</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
         <v>105</v>
       </c>
-      <c r="L72" t="n">
+      <c r="R72" t="n">
         <v>99</v>
       </c>
-      <c r="M72" t="n">
+      <c r="S72" t="n">
         <v>102</v>
       </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
-      <c r="O72" t="b">
-        <v>0</v>
-      </c>
-      <c r="P72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="b">
-        <v>1</v>
-      </c>
-      <c r="R72" t="inlineStr">
+      <c r="T72" t="b">
+        <v>0</v>
+      </c>
+      <c r="U72" t="b">
+        <v>0</v>
+      </c>
+      <c r="V72" t="b">
+        <v>0</v>
+      </c>
+      <c r="W72" t="b">
+        <v>1</v>
+      </c>
+      <c r="X72" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -8684,28 +10930,56 @@
           <t>e</t>
         </is>
       </c>
-      <c r="K73" t="n">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>子音</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>母音</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>LRL</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
         <v>99</v>
       </c>
-      <c r="L73" t="n">
+      <c r="R73" t="n">
         <v>67</v>
       </c>
-      <c r="M73" t="n">
+      <c r="S73" t="n">
         <v>83</v>
       </c>
-      <c r="N73" t="b">
-        <v>0</v>
-      </c>
-      <c r="O73" t="b">
-        <v>0</v>
-      </c>
-      <c r="P73" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="b">
-        <v>1</v>
-      </c>
-      <c r="R73" t="inlineStr">
+      <c r="T73" t="b">
+        <v>0</v>
+      </c>
+      <c r="U73" t="b">
+        <v>0</v>
+      </c>
+      <c r="V73" t="b">
+        <v>0</v>
+      </c>
+      <c r="W73" t="b">
+        <v>1</v>
+      </c>
+      <c r="X73" t="inlineStr">
         <is>
           <t>左右交互</t>
         </is>
@@ -12322,4 +14596,152 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>vowel_pattern</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>avg_interval</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>std_interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>106.8333333333333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.504384952922168</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CCV</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>88.33333333333333</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.85782801147531</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" t="n">
+        <v>148.5625</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128.6783411811422</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CVV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>136.6666666666667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>164.4410735390239</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VCC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>105</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20.14323707848369</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VCV</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C7" t="n">
+        <v>143.7962962962963</v>
+      </c>
+      <c r="D7" t="n">
+        <v>120.899215755812</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VVC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>161</v>
+      </c>
+      <c r="D8" t="n">
+        <v>157.9357464287297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>